--- a/chem/bromination_acetonelab.xlsx
+++ b/chem/bromination_acetonelab.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3aaf0ddacaed4ea8/Documents/CODE/CODE SUMMARY/chem/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A99D699-1177-4E41-99A6-D424D317BC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{5A99D699-1177-4E41-99A6-D424D317BC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B89EB22-9C67-49C7-A746-8CEE113A16DD}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="2630" windowWidth="18060" windowHeight="10200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bromination of Acetone" sheetId="1" r:id="rId1"/>
@@ -549,6 +549,26 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="525" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{64912464-A5CA-4FFB-89CF-399C0247D6EC}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200009404" version="1.0.0.8" store="wa200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K28"/>
